--- a/latex/求解/问题一/结果/result1.xlsx
+++ b/latex/求解/问题一/结果/result1.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B145"/>
+  <dimension ref="A1:B147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1875,6 +1875,26 @@
       </c>
       <c r="B145" t="n">
         <v>574.121</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>全天购电量</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>59482.699</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>全天购电费</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>35126.9486</v>
       </c>
     </row>
   </sheetData>
